--- a/resources/Part_3_Statistics/S18_L114/3.14.Confidence-intervals.Two-means.Independent-samples-Part-1-exercise.xlsx
+++ b/resources/Part_3_Statistics/S18_L114/3.14.Confidence-intervals.Two-means.Independent-samples-Part-1-exercise.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18229"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="CI, indep, var kwn" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Engineering</t>
   </si>
@@ -64,6 +64,39 @@
   </si>
   <si>
     <t>Compare it to the 95% confidence interval from the lesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 1: </t>
+  </si>
+  <si>
+    <t>Z statistics</t>
+  </si>
+  <si>
+    <t>1%-&gt;</t>
+  </si>
+  <si>
+    <t>alpha= 0,01</t>
+  </si>
+  <si>
+    <t>Z -&gt; 2,33</t>
+  </si>
+  <si>
+    <t>alpha/2= 0,005</t>
+  </si>
+  <si>
+    <t>Looking for: 0,995</t>
+  </si>
+  <si>
+    <t>-&gt; 2,58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">up to </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 2: </t>
+  </si>
+  <si>
+    <t>For a higher % of confidence, the interval is wider.</t>
   </si>
 </sst>
 </file>
@@ -143,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -175,6 +208,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,31 +490,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:N15"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:S15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="2"/>
-    <col min="8" max="8" width="5.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="2"/>
+    <col min="6" max="7" width="8.85546875" style="2"/>
+    <col min="8" max="8" width="5.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
@@ -489,7 +524,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -499,7 +534,7 @@
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -509,16 +544,16 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B7" s="1"/>
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.2">
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="2:14" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:19" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="6"/>
       <c r="C9" s="6" t="s">
         <v>0</v>
@@ -529,12 +564,36 @@
       <c r="E9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14"/>
+      <c r="G9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>16</v>
+      </c>
       <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-    </row>
-    <row r="10" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+      <c r="J9" s="19">
+        <v>0.99</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
@@ -547,12 +606,20 @@
       <c r="E10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="14"/>
+      <c r="G10" s="14">
+        <f>(C11-D11)-2.58*SQRT(C12^2/C10+D12^2/D10)</f>
+        <v>-10.005609042155303</v>
+      </c>
       <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-    </row>
-    <row r="11" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+      <c r="I10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="14">
+        <f>(C11-D11)+2.58*SQRT(C12^2/C10+D12^2/D10)</f>
+        <v>-3.9943909578446974</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
@@ -571,7 +638,7 @@
       <c r="I11" s="15"/>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B12" s="8" t="s">
         <v>4</v>
       </c>
@@ -585,21 +652,25 @@
         <f>SQRT((C12*C12/C10+D12*D12/D10))</f>
         <v>1.1649647450214351</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
+      <c r="G12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="I12" s="17"/>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:19" x14ac:dyDescent="0.2">
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
     </row>
-    <row r="14" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B14" s="1"/>
     </row>
-    <row r="15" spans="2:14" ht="12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B15" s="13"/>
       <c r="C15" s="14"/>
     </row>
